--- a/docs/files/REPORT_FILTRI/Agente - CR LICCIARDELLO AMANDA GINEVRA VERON.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR LICCIARDELLO AMANDA GINEVRA VERON.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -817,31 +817,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G11" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H11" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="I11" s="12" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente - CR LICCIARDELLO AMANDA GINEVRA VERON.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR LICCIARDELLO AMANDA GINEVRA VERON.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -841,7 +841,7 @@
         <v>61</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.7540983606557377</v>
+        <v>46</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente - CR LICCIARDELLO AMANDA GINEVRA VERON.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR LICCIARDELLO AMANDA GINEVRA VERON.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -817,31 +817,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
